--- a/data/data_monitoreo_otuzco.xlsx
+++ b/data/data_monitoreo_otuzco.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>151</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>148</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>116</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>115</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6">
@@ -487,27 +487,27 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>108</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SAUCEDO CABRERA CARLOS ALEXANDER</t>
+          <t>BECERRA ASMAT CAROL STEFANY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BECERRA ASMAT CAROL STEFANY</t>
+          <t>SAUCEDO CABRERA CARLOS ALEXANDER</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>85</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11">

--- a/data/data_monitoreo_otuzco.xlsx
+++ b/data/data_monitoreo_otuzco.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>208</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>173</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">

--- a/data/data_monitoreo_otuzco.xlsx
+++ b/data/data_monitoreo_otuzco.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>218</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4">
@@ -467,57 +467,57 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>183</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CORAS QUISPE JORGE AMERICO</t>
+          <t>MANOSALVA RUIZ SANDRA KAROLINE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MANOSALVA RUIZ SANDRA KAROLINE</t>
+          <t>CORAS QUISPE JORGE AMERICO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BECERRA ASMAT CAROL STEFANY</t>
+          <t>PACHECO ALISON</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>131</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SAUCEDO CABRERA CARLOS ALEXANDER</t>
+          <t>BECERRA ASMAT CAROL STEFANY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PACHECO ALISON</t>
+          <t>SAUCEDO CABRERA CARLOS ALEXANDER</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11">

--- a/data/data_monitoreo_otuzco.xlsx
+++ b/data/data_monitoreo_otuzco.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>227</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>214</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>193</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>177</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>172</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7">
@@ -497,27 +497,27 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>148</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BECERRA ASMAT CAROL STEFANY</t>
+          <t>SAUCEDO CABRERA CARLOS ALEXANDER</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>136</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SAUCEDO CABRERA CARLOS ALEXANDER</t>
+          <t>BECERRA ASMAT CAROL STEFANY</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>119</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">

--- a/data/data_monitoreo_otuzco.xlsx
+++ b/data/data_monitoreo_otuzco.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>198</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7">
@@ -497,27 +497,27 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SAUCEDO CABRERA CARLOS ALEXANDER</t>
+          <t>BECERRA ASMAT CAROL STEFANY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>149</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BECERRA ASMAT CAROL STEFANY</t>
+          <t>SAUCEDO CABRERA CARLOS ALEXANDER</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10">
